--- a/etf_holdings/2026-08-31_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:50</t>
+          <t>2026-08-31 00:57:01</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:51</t>
+          <t>2026-08-31 00:57:02</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:53</t>
+          <t>2026-08-31 00:57:04</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:54</t>
+          <t>2026-08-31 00:57:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:54</t>
+          <t>2026-08-31 00:57:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:54</t>
+          <t>2026-08-31 00:57:05</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:54</t>
+          <t>2026-08-31 00:57:05</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:54</t>
+          <t>2026-08-31 00:57:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 00:37:54</t>
+          <t>2026-08-31 00:57:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-31_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,33 +509,33 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.41%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.29%11,264,000</t>
+          <t>9.38%11,014,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.29%</t>
+          <t>9.38%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11264000</v>
+        <v>11014000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,33 +570,33 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0%5490</t>
+          <t>-0.09%5485</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5490</v>
+        <v>5485</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.99%4,807,000</t>
+          <t>9.24%4,757,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.99%</t>
+          <t>9.24%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4807000</v>
+        <v>4757000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-5.93%1110</t>
+          <t>+1.93%3425</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-5.93%</t>
+          <t>+1.93%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1110</v>
+        <v>3425</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.68%20,300,000</t>
+          <t>7.21%5,949,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.68%</t>
+          <t>7.21%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>20300000</v>
+        <v>5949000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.49%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+3.1%3985</t>
+          <t>-10%999</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3985</v>
+        <v>999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.99%5,148,000</t>
+          <t>7.18%20,300,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.99%</t>
+          <t>7.18%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5148000</v>
+        <v>20300000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.78%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.6%3360</t>
+          <t>-1.51%3925</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.6%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3360</v>
+        <v>3925</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.85%5,979,000</t>
+          <t>7.07%5,088,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.85%</t>
+          <t>7.07%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5979000</v>
+        <v>5088000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,33 +814,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+5.65%7200</t>
+          <t>-1.46%7095</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+5.65%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>7200</v>
+        <v>7095</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.46%2,226,000</t>
+          <t>5.47%2,176,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.46%</t>
+          <t>5.47%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2226000</v>
+        <v>2176000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+7.57%597</t>
+          <t>+3.54%5990</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+7.57%</t>
+          <t>+3.54%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>597</v>
+        <v>5990</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.17%25,387,000</t>
+          <t>5.08%2,397,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.17%</t>
+          <t>5.08%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>25387000</v>
+        <v>2397000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+2.48%5785</t>
+          <t>-8.71%545</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>-8.71%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5785</v>
+        <v>545</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.75%2,407,000</t>
+          <t>4.82%24,987,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>4.82%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2407000</v>
+        <v>24987000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+1.67%2125</t>
+          <t>+0.55%1840</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>+0.55%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2125</v>
+        <v>1840</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.75%6,564,000</t>
+          <t>4.72%7,240,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>4.72%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>6564000</v>
+        <v>7240000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+3.39%1830</t>
+          <t>-4.24%2035</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+3.39%</t>
+          <t>-4.24%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1830</v>
+        <v>2035</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.52%7,250,000</t>
+          <t>4.66%6,464,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.52%</t>
+          <t>4.66%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>7250000</v>
+        <v>6464000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,33 +1119,33 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.18%5030</t>
+          <t>+1.99%5130</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.18%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5030</v>
+        <v>5130</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.26%2,486,000</t>
+          <t>4.50%2,476,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.26%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2486000</v>
+        <v>2476000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.64%621</t>
+          <t>-0.81%1230</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.64%</t>
+          <t>-0.81%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>621</v>
+        <v>1230</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.12%19,479,000</t>
+          <t>4.13%9,474,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.12%</t>
+          <t>4.13%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>19479000</v>
+        <v>9474000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,25 +1236,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.25%1240</t>
+          <t>-0.77%129</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.25%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1240</v>
+        <v>129</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4.07%9,624,000</t>
+          <t>4.07%89,118,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1263,11 +1263,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>9624000</v>
+        <v>89118000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+9.7%130</t>
+          <t>-5.96%584</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+9.7%</t>
+          <t>-5.96%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>130</v>
+        <v>584</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.97%89,518,000</t>
+          <t>3.86%18,679,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.97%</t>
+          <t>3.86%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>89518000</v>
+        <v>18679000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:01</t>
+          <t>2026-08-31 19:29:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,33 +1363,33 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+9.98%2260</t>
+          <t>-3.98%2170</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>-3.98%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2260</v>
+        <v>2170</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.60%4,671,848</t>
+          <t>3.53%4,591,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>3.53%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>4671848</v>
+        <v>4591848</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,35 +1424,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+3.11%1490</t>
+          <t>-3.69%1435</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+3.11%</t>
+          <t>-3.69%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.79%5,498,000</t>
+          <t>2.74%5,398,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>5498000</v>
+        <v>5398000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+5.39%2345</t>
+          <t>-1.71%2305</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+5.39%</t>
+          <t>-1.71%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.81%2,264,000</t>
+          <t>1.41%1,731,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>2264000</v>
+        <v>1731000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,35 +1550,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+2.12%15630</t>
+          <t>+2.78%16065</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+2.12%</t>
+          <t>+2.78%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.67%313,900</t>
+          <t>1.18%207,900</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.67%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>313900</v>
+        <v>207900</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,22 +1613,22 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+9.09%270</t>
+          <t>-4.81%257</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+9.09%</t>
+          <t>-4.81%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>257</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.17%12,668,450</t>
+          <t>1.17%12,818,450</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>12668450</v>
+        <v>12818450</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,35 +1676,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+3.13%990</t>
+          <t>-2.12%969</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>-2.12%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>969</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.84%2,477,000</t>
+          <t>0.83%2,427,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2477000</v>
+        <v>2427000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1734,40 +1734,40 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+9.71%1130</t>
+          <t>+1.41%6100</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+9.71%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>6100</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.75%1,957,000</t>
+          <t>0.70%325,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1957000</v>
+        <v>325000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1797,40 +1797,40 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+1.6%6015</t>
+          <t>-0.16%609</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+1.6%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>609</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.67%325,000</t>
+          <t>0.68%3,173,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.68%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>325000</v>
+        <v>3173000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,40 +1860,40 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.13%610</t>
+          <t>+3.1%1165</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.66%3,173,000</t>
+          <t>0.60%1,457,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>3173000</v>
+        <v>1457000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1928,35 +1928,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.44%1265</t>
+          <t>-7.11%1175</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>-7.11%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.56%1,301,000</t>
+          <t>0.54%1,300,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1301000</v>
+        <v>1300000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1991,35 +1991,35 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+7.06%235</t>
+          <t>-2.98%228</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+7.06%</t>
+          <t>-2.98%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>228</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.47%5,917,000</t>
+          <t>0.48%5,916,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>5917000</v>
+        <v>5916000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2054,27 +2054,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.19%2680</t>
+          <t>+6.16%2845</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.19%</t>
+          <t>+6.16%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2680</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.44%477,000</t>
+          <t>0.48%477,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.48%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2117,35 +2117,35 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.73%480.5</t>
+          <t>+4.06%500</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>+4.06%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>480.5</t>
+          <t>500</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.27%1,645,000</t>
+          <t>0.29%1,644,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.29%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1645000</v>
+        <v>1644000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2180,31 +2180,31 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.18%201.5</t>
+          <t>-0.99%199.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.18%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>201.5</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.22%3,249,000</t>
+          <t>0.23%3,248,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3249000</v>
+        <v>3248000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:02</t>
+          <t>2026-08-31 19:29:49</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2243,35 +2243,35 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+2.38%215</t>
+          <t>-1.4%212</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+2.38%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>215</t>
+          <t>212</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.16%2,223,000</t>
+          <t>0.17%2,222,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2223000</v>
+        <v>2222000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2306,20 +2306,20 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+3.33%217</t>
+          <t>-1.38%214</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+3.33%</t>
+          <t>-1.38%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.13%1,741,000</t>
+          <t>0.13%1,740,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2328,11 +2328,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1741000</v>
+        <v>1740000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2367,16 +2367,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.93%84.7</t>
+          <t>-1.18%83.7</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>84.7</v>
+        <v>83.7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2423,25 +2423,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-4.55%1365</t>
+          <t>+3.11%248.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-4.55%</t>
+          <t>+3.11%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1365</v>
+        <v>248.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.04%88,000</t>
+          <t>0.04%501,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2450,11 +2450,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>88000</v>
+        <v>501000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.52%19.05</t>
+          <t>-0.52%18.95</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>19.05</v>
+        <v>18.95</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2550,16 +2550,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+9.92%543</t>
+          <t>-0.55%540</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2611,16 +2611,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+5.04%4065</t>
+          <t>+0.25%4075</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+5.04%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>4065</v>
+        <v>4075</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2672,16 +2672,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.26%78.5</t>
+          <t>+0.38%78.8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>78.5</v>
+        <v>78.8</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,16 +2733,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-4.39%1415</t>
+          <t>+0.71%1425</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-4.39%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1415</v>
+        <v>1425</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2794,16 +2794,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+2.17%7065</t>
+          <t>+8.28%7650</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+8.28%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>7065</v>
+        <v>7650</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2855,16 +2855,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.3%332.5</t>
+          <t>+1.8%338.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+1.8%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>332.5</v>
+        <v>338.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2911,25 +2911,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.18%540</t>
+          <t>-1.47%1345</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>-1.47%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>540</v>
+        <v>1345</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0%8,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2972,21 +2972,21 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2637慧洋-KY</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.64%92.1</t>
+          <t>+0.56%543</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>92.09999999999999</v>
+        <v>543</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3033,21 +3033,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>2637慧洋-KY</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+2.38%6250</t>
+          <t>+2.17%94.1</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+2.38%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6250</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3094,21 +3094,21 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+1.01%2010</t>
+          <t>+0.56%6285</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+1.01%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2010</v>
+        <v>6285</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:04</t>
+          <t>2026-08-31 19:29:50</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3155,21 +3155,21 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.46%972</t>
+          <t>-2.49%1960</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>972</v>
+        <v>1960</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:05</t>
+          <t>2026-08-31 19:29:52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3216,21 +3216,21 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4966譜瑞-KY</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.02%584</t>
+          <t>-6.17%912</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.02%</t>
+          <t>-6.17%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>584</v>
+        <v>912</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:05</t>
+          <t>2026-08-31 19:29:52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3277,21 +3277,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>4966譜瑞-KY</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.23%241</t>
+          <t>-1.03%578</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.23%</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>241</v>
+        <v>578</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:05</t>
+          <t>2026-08-31 19:29:52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3343,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+0.22%90.5</t>
+          <t>-1.55%89.1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>-1.55%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>90.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:05</t>
+          <t>2026-08-31 19:29:52</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,16 +3404,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.4%253</t>
+          <t>-1.19%250</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-1.19%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:05</t>
+          <t>2026-08-31 19:29:52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3465,16 +3465,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1.32%153</t>
+          <t>-0.98%151.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>153</v>
+        <v>151.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 00:57:05</t>
+          <t>2026-08-31 19:29:52</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3526,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+5.12%154</t>
+          <t>-1.95%151</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+5.12%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-31_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-31_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:45</t>
+          <t>2026-08-31 22:11:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:49</t>
+          <t>2026-08-31 22:11:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:50</t>
+          <t>2026-08-31 22:11:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:52</t>
+          <t>2026-08-31 22:12:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:52</t>
+          <t>2026-08-31 22:12:10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:52</t>
+          <t>2026-08-31 22:12:10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:52</t>
+          <t>2026-08-31 22:12:10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:52</t>
+          <t>2026-08-31 22:12:10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-31 19:29:52</t>
+          <t>2026-08-31 22:12:10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
